--- a/stick-world/config/excel/编制预设.xlsx
+++ b/stick-world/config/excel/编制预设.xlsx
@@ -2,40 +2,196 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27360" windowHeight="17205" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="presets" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="编制预设" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="23">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
@@ -44,12 +200,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -58,26 +394,306 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -430,7 +1046,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -440,13 +1055,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="100" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,83 +1074,654 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>name_zh</t>
+          <t>preset</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>tag</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>preset_data_json</t>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>parent_id</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>标签</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>预设数据JSON</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>唯一ID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>所属预设</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>层级名称</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>层级号(L5最高)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>父级ID</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>org_preset_military</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>标准军事编制</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>military</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>{"tiers":[{"name":"师","level":4,"children":[{"name":"团","level":3,"subdivisions":3,"children":[{"name":"连","level":2,"subdivisions":4,"children":[{"name":"排","level":1,"subdivisions":4,"children":[]}]}]}]}]}</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tier_division</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>军事编制</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>师</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>org_preset_academy</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>科学院架构</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>{"tiers":[{"name":"科学院","level":5,"children":[{"name":"研究所","level":4,"subdivisions":5,"children":[{"name":"研究室","level":3,"subdivisions":4,"children":[{"name":"课题组","level":2,"subdivisions":3,"children":[]}]}]}]}]}</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tier_regiment</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>军事编制</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>团</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>tier_division</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tier_battalion</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>军事编制</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>营</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>tier_regiment</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tier_company</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>军事编制</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>连</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>tier_battalion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tier_platoon</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>军事编制</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>排</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>tier_company</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tier_academy</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>科研架构</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>科学院</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tier_institute</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>科研架构</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>研究院</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>tier_academy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tier_research_center</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>科研架构</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>tier_institute</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tier_lab</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>科研架构</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>研究室</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>tier_research_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tier_research_group</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>科研架构</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>课题组</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>tier_lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tier_engineering_academy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>工程架构</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>工程院</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tier_engineering_institute</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>工程架构</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>工程所</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>tier_engineering_academy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tier_project_team</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>工程架构</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>项目组</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>tier_engineering_institute</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tier_construction_crew</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>工程架构</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>施工队</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>tier_project_team</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tier_construction_squad</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>工程架构</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>施工分队</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>tier_construction_crew</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tier_empire</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>行政架构</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>帝国</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tier_region</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>行政架构</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>tier_empire</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tier_province</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>行政架构</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>省份</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>tier_region</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tier_city</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>行政架构</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>tier_province</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>tier_tribe</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>行政架构</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>部落</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>tier_city</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tier_logistics_hq</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>运输架构</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>总物流中心</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>tier_logistics_center</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>运输架构</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>物流中心</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>tier_logistics_hq</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>tier_transfer_station</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>运输架构</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>中转站</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>tier_logistics_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>tier_transport_convoy</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>运输架构</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>运输队</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>tier_transfer_station</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>tier_transport_squad</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>运输架构</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>运输分队</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>tier_transport_convoy</t>
         </is>
       </c>
     </row>

--- a/stick-world/config/excel/编制预设.xlsx
+++ b/stick-world/config/excel/编制预设.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27360" windowHeight="17205" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="编制预设" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="presets" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1055,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1067,84 +1067,70 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#output_dir: formations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>preset</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>parent_id</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>唯一ID</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>所属预设</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>层级名称</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>层级号(L5最高)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>父级ID</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>tier_division</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>军事编制</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>师</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tier_regiment</t>
+          <t>tier_division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1154,22 +1140,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>团</t>
+          <t>师</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>tier_division</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tier_battalion</t>
+          <t>tier_regiment</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1179,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>营</t>
+          <t>团</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>tier_regiment</t>
+          <t>tier_division</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tier_company</t>
+          <t>tier_battalion</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1204,22 +1185,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>连</t>
+          <t>营</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tier_battalion</t>
+          <t>tier_regiment</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tier_platoon</t>
+          <t>tier_company</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1229,43 +1210,47 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>排</t>
+          <t>连</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tier_company</t>
+          <t>tier_battalion</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tier_academy</t>
+          <t>tier_platoon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>科研架构</t>
+          <t>军事编制</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>科学院</t>
+          <t>排</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>tier_company</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tier_institute</t>
+          <t>tier_academy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1275,22 +1260,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>研究院</t>
+          <t>科学院</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>tier_academy</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tier_research_center</t>
+          <t>tier_institute</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1300,22 +1280,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>研究院</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tier_institute</t>
+          <t>tier_academy</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tier_lab</t>
+          <t>tier_research_center</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1325,22 +1305,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>研究室</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>tier_research_center</t>
+          <t>tier_institute</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tier_research_group</t>
+          <t>tier_lab</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1350,43 +1330,47 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>课题组</t>
+          <t>研究室</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>tier_lab</t>
+          <t>tier_research_center</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tier_engineering_academy</t>
+          <t>tier_research_group</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>工程架构</t>
+          <t>科研架构</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>工程院</t>
+          <t>课题组</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>tier_lab</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tier_engineering_institute</t>
+          <t>tier_engineering_academy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1396,22 +1380,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>工程所</t>
+          <t>工程院</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>tier_engineering_academy</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tier_project_team</t>
+          <t>tier_engineering_institute</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1421,22 +1400,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>项目组</t>
+          <t>工程所</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>tier_engineering_institute</t>
+          <t>tier_engineering_academy</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tier_construction_crew</t>
+          <t>tier_project_team</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1446,22 +1425,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>施工队</t>
+          <t>项目组</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>tier_project_team</t>
+          <t>tier_engineering_institute</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tier_construction_squad</t>
+          <t>tier_construction_crew</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1471,43 +1450,47 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>施工分队</t>
+          <t>施工队</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>tier_construction_crew</t>
+          <t>tier_project_team</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tier_empire</t>
+          <t>tier_construction_squad</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>行政架构</t>
+          <t>工程架构</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>帝国</t>
+          <t>施工分队</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>tier_construction_crew</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tier_region</t>
+          <t>tier_empire</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1517,22 +1500,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>帝国</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>tier_empire</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tier_province</t>
+          <t>tier_region</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1542,22 +1520,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>省份</t>
+          <t>地区</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>tier_region</t>
+          <t>tier_empire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tier_city</t>
+          <t>tier_province</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1567,22 +1545,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>城市</t>
+          <t>省份</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>tier_province</t>
+          <t>tier_region</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tier_tribe</t>
+          <t>tier_city</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1592,43 +1570,47 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>部落</t>
+          <t>城市</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>tier_city</t>
+          <t>tier_province</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tier_logistics_hq</t>
+          <t>tier_tribe</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>运输架构</t>
+          <t>行政架构</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>总物流中心</t>
+          <t>部落</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>tier_city</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tier_logistics_center</t>
+          <t>tier_logistics_hq</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1638,22 +1620,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>物流中心</t>
+          <t>总物流中心</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>tier_logistics_hq</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tier_transfer_station</t>
+          <t>tier_logistics_center</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1663,22 +1640,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>中转站</t>
+          <t>物流中心</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>tier_logistics_center</t>
+          <t>tier_logistics_hq</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tier_transport_convoy</t>
+          <t>tier_transfer_station</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1688,38 +1665,63 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>运输队</t>
+          <t>中转站</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>tier_transfer_station</t>
+          <t>tier_logistics_center</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>tier_transport_convoy</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>运输架构</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>运输队</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>tier_transfer_station</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>tier_transport_squad</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>运输架构</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>运输分队</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D28" t="n">
         <v>1</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>tier_transport_convoy</t>
         </is>
